--- a/VerveStacks_DEU_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_DEU_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1E0213-B702-4607-87D5-A3A4BD4E04D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74DA53BC-05B8-4565-89B5-A1608F7EABFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8009,7 +8009,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{900FF55A-2375-4D3E-9764-2CE748A6098F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79D92F29-44E7-4C86-89FD-88136BD019B7}">
   <dimension ref="B3:H485"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_DEU_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_DEU_grids_kan/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74DA53BC-05B8-4565-89B5-A1608F7EABFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB94BFC0-F85A-4475-A289-C01F4F39FB91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="12682" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -8009,7 +8009,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79D92F29-44E7-4C86-89FD-88136BD019B7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A23C81DC-C18E-4EA1-973C-E6F21EE6A444}">
   <dimension ref="B3:H485"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_DEU_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_DEU_grids_kan/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB94BFC0-F85A-4475-A289-C01F4F39FB91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE16CF2-BD32-408B-A893-31ED0808E198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="12682" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -8009,7 +8009,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A23C81DC-C18E-4EA1-973C-E6F21EE6A444}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28F8C3FA-E784-4295-9753-57F3F1A64AD5}">
   <dimension ref="B3:H485"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
